--- a/BWI/bestwine_output/bestwine_Thailand.xlsx
+++ b/BWI/bestwine_output/bestwine_Thailand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA123"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13791,6 +13791,430 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Vanichwathana (bangkok) Company Limited</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Vanichwathana (bangkok) Company Limited</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>22283</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Khet Samphanthawong</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>37-43 Anuwong Road</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>10100</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vanichwathana.com</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>sales@vanichwathana.com</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 221 5354</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>0105513002646</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr"/>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr"/>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>Chalan Kanchanasevee</t>
+        </is>
+      </c>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Manager</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr"/>
+      <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chalan-kanchanasevee-39782b166/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Wine-ari Shop Company Limited</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Wine-ari Shop Company Limited</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>121987</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Khet Phaya Thai</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Pradiphat Soi 1</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>10400</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>https://wineari.com</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>zoltan@wineari.com</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>0105565076039</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr"/>
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineARIshop/</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winearishop/</t>
+        </is>
+      </c>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr"/>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>Zoltan</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>Wine Curator</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Italasia Trading (thailand) Company Limited</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Italasia Trading (thailand) Company Limited</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>13608</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Khet Watthana</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>253 Sukhumvit 21 Road</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>10110</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://italasiagroup.com, https://www.italasiaphuket.com</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>contactus@italasiagroup.com</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 261 7990</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>0105539015397</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italasia-group/</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italasiakrabi/</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/italasiagroup</t>
+        </is>
+      </c>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr"/>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>Thierry Berno</t>
+        </is>
+      </c>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>Head Of The Wine</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thierryberno/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Italasia Trading (thailand) Company Limited</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Italasia Trading (thailand) Company Limited</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>13608</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Khet Watthana</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>253 Sukhumvit 21 Road</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>10110</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>https://italasiagroup.com, https://www.italasiaphuket.com</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>contactus@italasiagroup.com</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 261 7990</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>0105539015397</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italasia-group/</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italasiakrabi/</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/italasiagroup</t>
+        </is>
+      </c>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>Parviza Barakaeva</t>
+        </is>
+      </c>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/parviza-barakaeva-824714101/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Thailand.xlsx
+++ b/BWI/bestwine_output/bestwine_Thailand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA127"/>
+  <dimension ref="A1:AA132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -14215,6 +14215,523 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Bacchus Global Company Limited</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Bacchus Global Company Limited</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>27205</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Wattana</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>36/20 Sukhumvit 39, Sukhumvit Rd. Klongton Nua</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>10110</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://bacchusglobal.co.th</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>info@bacchusglobal.co.th</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 662 6176</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>0105556026270</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr"/>
+      <c r="S128" s="2" t="inlineStr"/>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bacchus/</t>
+        </is>
+      </c>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr"/>
+      <c r="X128" s="2" t="inlineStr"/>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Vanichwathana (bangkok) Company Limited</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Vanichwathana (bangkok) Company Limited</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>22283</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Khet Samphanthawong</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>37-43 Anuwong Road</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>10100</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vanichwathana.com</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>sales@vanichwathana.com</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 221 5354</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>0105513002646</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr"/>
+      <c r="S129" s="2" t="inlineStr"/>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
+          <t>Chalan Kanchanasevee</t>
+        </is>
+      </c>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>Assistant Manager</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chalan-kanchanasevee-39782b166/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Wine-ari Shop Company Limited</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Wine-ari Shop Company Limited</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>121987</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Khet Phaya Thai</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Pradiphat Soi 1</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>10400</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://wineari.com</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>zoltan@wineari.com</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr"/>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>0105565076039</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr"/>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineARIshop/</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winearishop/</t>
+        </is>
+      </c>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>Zoltan</t>
+        </is>
+      </c>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>Wine Curator</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Italasia Trading (thailand) Company Limited</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Italasia Trading (thailand) Company Limited</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>13608</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Khet Watthana</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>253 Sukhumvit 21 Road</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>10110</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>https://italasiagroup.com, https://www.italasiaphuket.com</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>contactus@italasiagroup.com</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 261 7990</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>0105539015397</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italasia-group/</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italasiakrabi/</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/italasiagroup</t>
+        </is>
+      </c>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>Thierry Berno</t>
+        </is>
+      </c>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>Head Of The Wine</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/thierryberno/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Italasia Trading (thailand) Company Limited</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Italasia Trading (thailand) Company Limited</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>13608</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Khet Watthana</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>253 Sukhumvit 21 Road</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>10110</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://italasiagroup.com, https://www.italasiaphuket.com</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>contactus@italasiagroup.com</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 261 7990</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>0105539015397</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/italasia-group/</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/italasiakrabi/</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/italasiagroup</t>
+        </is>
+      </c>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>Parviza Barakaeva</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/parviza-barakaeva-824714101/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Thailand.xlsx
+++ b/BWI/bestwine_output/bestwine_Thailand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA132"/>
+  <dimension ref="A1:AA133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -14732,6 +14732,103 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Cititex Group</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Cititex Group</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>29335</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Khet Bang Bon</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>8 Kanchanaphisek Road</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cititex.co.th</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>cititex@cititex.co.th</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 895 1761</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>0105549053682</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr"/>
+      <c r="S133" s="2" t="inlineStr"/>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>Sithisak Chatamornwong</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sithisak-chatamornwong-6970567a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Thailand.xlsx
+++ b/BWI/bestwine_output/bestwine_Thailand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA133"/>
+  <dimension ref="A1:AA134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -14829,6 +14829,103 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Cititex Group</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Cititex Group</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>29335</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Khet Bang Bon</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>8 Kanchanaphisek Road</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cititex.co.th</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>cititex@cititex.co.th</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 895 1761</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>0105549053682</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr"/>
+      <c r="S134" s="2" t="inlineStr"/>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>Sithisak Chatamornwong</t>
+        </is>
+      </c>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sithisak-chatamornwong-6970567a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Thailand.xlsx
+++ b/BWI/bestwine_output/bestwine_Thailand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA134"/>
+  <dimension ref="A1:AA135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -14926,6 +14926,103 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Cititex Group</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Cititex Group</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>29335</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Khet Bang Bon</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>8 Kanchanaphisek Road</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cititex.co.th</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>cititex@cititex.co.th</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 895 1761</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>0105549053682</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr"/>
+      <c r="S135" s="2" t="inlineStr"/>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>Sithisak Chatamornwong</t>
+        </is>
+      </c>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sithisak-chatamornwong-6970567a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Thailand.xlsx
+++ b/BWI/bestwine_output/bestwine_Thailand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA135"/>
+  <dimension ref="A1:AA136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15023,6 +15023,103 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Cititex Group</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Cititex Group</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>29335</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Khet Bang Bon</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>8 Kanchanaphisek Road</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cititex.co.th</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>cititex@cititex.co.th</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 895 1761</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>0105549053682</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr"/>
+      <c r="S136" s="2" t="inlineStr"/>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr">
+        <is>
+          <t>Sithisak Chatamornwong</t>
+        </is>
+      </c>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sithisak-chatamornwong-6970567a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Thailand.xlsx
+++ b/BWI/bestwine_output/bestwine_Thailand.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA136"/>
+  <dimension ref="A1:AA137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -15120,6 +15120,103 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Cititex Group</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Cititex Group</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>29335</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Khet Bang Bon</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Krung Thep Maha Nakhon</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>8 Kanchanaphisek Road</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cititex.co.th</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>cititex@cititex.co.th</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>+66 2 895 1761</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>0105549053682</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr"/>
+      <c r="S137" s="2" t="inlineStr"/>
+      <c r="T137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>Sithisak Chatamornwong</t>
+        </is>
+      </c>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sithisak-chatamornwong-6970567a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
